--- a/data/script.xlsx
+++ b/data/script.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Harbour Presenter 係粵語優先嘅語音簡報代理。佢跟預先寫好嘅稿講，唔會即場生稿。n8n 負責節奏，桌面 PowerPoint 跟住翻頁。觀眾一打斷，可以跳去相關一頁再接返。</t>
+          <t>Harbour Presenter 係粵語優先嘅語音簡報代理。佢跟預先寫好嘅稿講，唔會即場生稿。本機導演負責節奏，桌面 PowerPoint 跟住翻頁。觀眾一打斷，可以跳去相關一頁再接返。</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Harbour Presenter is a Cantonese-first voice presenter. It reads a prepared script; it does not invent the talk. n8n directs pacing; desktop PowerPoint follows. After an interruption it can jump to the matching slide and resume.</t>
+          <t>Harbour Presenter is a Cantonese-first voice presenter. It reads a prepared script; it does not invent the talk. The local director controls pacing; desktop PowerPoint follows. After an interruption it can jump to the matching slide and resume.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
